--- a/datos/ejemplos/insumo-producto-ambiental.xlsx
+++ b/datos/ejemplos/insumo-producto-ambiental.xlsx
@@ -11,29 +11,19 @@
     <sheet name="Modelo Insumo-Producto" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Info" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName function="false" hidden="false" name="A" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="AINV" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="Anew" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="b" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="Calculated_Relationship_HS12___HS07" vbProcedure="false">'[1]Correlation HS2012-HS2007'!#REF!</definedName>
     <definedName function="false" hidden="false" name="CMAT" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="COEF" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="deltafnew" vbProcedure="false">#REF!</definedName>
-    <definedName function="false" hidden="false" name="eprime" vbProcedure="false">'Modelo Insumo-Producto'!$C$36:$D$36</definedName>
+    <definedName function="false" hidden="false" name="deltafnew" vbProcedure="false">'Modelo Insumo-Producto'!$C$56:$C$57</definedName>
     <definedName function="false" hidden="false" name="fdem" vbProcedure="false">'Modelo Insumo-Producto'!$E$4:$E$5</definedName>
-    <definedName function="false" hidden="false" name="fdemnew" vbProcedure="false">#REF!</definedName>
-    <definedName function="false" hidden="false" name="go_level_top1" vbProcedure="false">OFFSET('[2]35-sector'!$E$36,MATCH(#ref!,'[2]35-sector'!$E$37:$E$71,0),2,1,8)</definedName>
+    <definedName function="false" hidden="false" name="fdemnew" vbProcedure="false">'Modelo Insumo-Producto'!$C$33:$C$34</definedName>
     <definedName function="false" hidden="false" name="gprime" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="GPRIMEHAT" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="GPRIMEHATINV" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="HS" vbProcedure="false">'[3]HS02_CPC1.1_SITC3_ISIC3.1 (2)'!#REF!</definedName>
     <definedName function="false" hidden="false" name="I" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="identity" vbProcedure="false">'Modelo Insumo-Producto'!$C$21:$D$22</definedName>
     <definedName function="false" hidden="false" name="IP" vbProcedure="false">#ref!</definedName>
@@ -42,59 +32,23 @@
     <definedName function="false" hidden="false" name="L" vbProcedure="false">'Modelo Insumo-Producto'!$C$27:$D$28</definedName>
     <definedName function="false" hidden="false" name="Lnew" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="M" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="M1_stone" vbProcedure="false">'[2]2000'!$E$1382:$BV$1451</definedName>
-    <definedName function="false" hidden="false" name="M2_stone" vbProcedure="false">'[2]2000'!$E$1524:$BV$1593</definedName>
-    <definedName function="false" hidden="false" name="M3_stone" vbProcedure="false">'[2]2000'!$E$1737:$BV$1806</definedName>
     <definedName function="false" hidden="false" name="Matrix1" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="N" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="O" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="Q" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2010" vbProcedure="false">'[4]13-sector VAX_G_2010'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2011" vbProcedure="false">'[4]13-sector VAX_G_2011'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2012" vbProcedure="false">'[4]13-sector VAX_G_2012'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2013" vbProcedure="false">'[4]13-sector VAX_G_2013'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2014" vbProcedure="false">'[4]13-sector VAX_G_2014'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2015" vbProcedure="false">'[4]13-sector VAX_G_2015'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2016" vbProcedure="false">'[4]13-sector VAX_G_2016'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_trad_2017" vbProcedure="false">'[4]13-sector VAX_G_2017'!$C$141:$P$203</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2010" vbProcedure="false">'[4]13-sector VAX_G_2010'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2011" vbProcedure="false">'[4]13-sector VAX_G_2011'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2012" vbProcedure="false">'[4]13-sector VAX_G_2012'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2013" vbProcedure="false">'[4]13-sector VAX_G_2013'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2014" vbProcedure="false">'[4]13-sector VAX_G_2014'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2015" vbProcedure="false">'[4]13-sector VAX_G_2015'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2016" vbProcedure="false">'[4]13-sector VAX_G_2016'!$C$209:$P$271</definedName>
-    <definedName function="false" hidden="false" name="rca_vax_2017" vbProcedure="false">'[4]13-sector VAX_G_2017'!$C$209:$P$271</definedName>
     <definedName function="false" hidden="false" name="REQ" vbProcedure="false">'Modelo Insumo-Producto'!$C$18:$D$19</definedName>
     <definedName function="false" hidden="false" name="S" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="Sectors" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" name="sector_list" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="SUNBURST" vbProcedure="false">'[4]35-sector'!#REF!</definedName>
     <definedName function="false" hidden="false" name="TM" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2010" vbProcedure="false">'[4]13-sector VAX_G_2010'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2011" vbProcedure="false">'[4]13-sector VAX_G_2011'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2012" vbProcedure="false">'[4]13-sector VAX_G_2012'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2013" vbProcedure="false">'[4]13-sector VAX_G_2013'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2014" vbProcedure="false">'[4]13-sector VAX_G_2014'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2015" vbProcedure="false">'[4]13-sector VAX_G_2015'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2016" vbProcedure="false">'[4]13-sector VAX_G_2016'!$T$5:$AI$67</definedName>
-    <definedName function="false" hidden="false" name="vax_g_2017" vbProcedure="false">'[4]13-sector VAX_G_2017'!$T$5:$AI$67</definedName>
     <definedName function="false" hidden="false" name="xhat" vbProcedure="false">'Modelo Insumo-Producto'!$C$12:$D$13</definedName>
     <definedName function="false" hidden="false" name="xhatinv" vbProcedure="false">'Modelo Insumo-Producto'!$C$15:$D$16</definedName>
-    <definedName function="false" hidden="false" name="xnew" vbProcedure="false">#REF!</definedName>
-    <definedName function="false" hidden="false" name="xnewdiag" vbProcedure="false">#REF!</definedName>
+    <definedName function="false" hidden="false" name="xnew" vbProcedure="false">'Modelo Insumo-Producto'!$C$36:$C$37</definedName>
+    <definedName function="false" hidden="false" name="xnewdiag" vbProcedure="false">'Modelo Insumo-Producto'!$C$39:$D$40</definedName>
     <definedName function="false" hidden="false" name="xoriginal" vbProcedure="false">'Modelo Insumo-Producto'!$G$4:$G$5</definedName>
-    <definedName function="false" hidden="false" name="x_2010" vbProcedure="false">'[4]13-sector VAX_G_2010'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2011" vbProcedure="false">'[4]13-sector VAX_G_2011'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2012" vbProcedure="false">'[4]13-sector VAX_G_2012'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2013" vbProcedure="false">'[4]13-sector VAX_G_2013'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2014" vbProcedure="false">'[4]13-sector VAX_G_2014'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2015" vbProcedure="false">'[4]13-sector VAX_G_2015'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2016" vbProcedure="false">'[4]13-sector VAX_G_2016'!$C$5:$R$67</definedName>
-    <definedName function="false" hidden="false" name="x_2017" vbProcedure="false">'[4]13-sector VAX_G_2017'!$C$5:$R$67</definedName>
     <definedName function="false" hidden="false" name="Z" vbProcedure="false">'Modelo Insumo-Producto'!$C$4:$D$5</definedName>
     <definedName function="false" hidden="false" name="ZETA" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="Znew" vbProcedure="false">#REF!</definedName>
+    <definedName function="false" hidden="false" name="Znew" vbProcedure="false">'Modelo Insumo-Producto'!$C$42:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -105,30 +59,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t xml:space="preserve">Agricultura</t>
   </si>
@@ -172,10 +104,52 @@
     <t xml:space="preserve">Calibración</t>
   </si>
   <si>
+    <t xml:space="preserve">Nueva Demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L * Fnew = Xnew =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xnueva diag =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A * xnueva diag =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Znueva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuevo cuadro insumo-producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastos totales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambios en lugar de niveles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deltafnueva =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deltaxnueva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo de cambio tc =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lcf =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f en moneda local</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extensión ambiental</t>
   </si>
   <si>
-    <t xml:space="preserve">eprime = </t>
+    <t xml:space="preserve">eprima = </t>
   </si>
   <si>
     <t xml:space="preserve">(emisiones CO2)</t>
@@ -184,26 +158,109 @@
     <t xml:space="preserve">epsilonprime =</t>
   </si>
   <si>
+    <t xml:space="preserve">Epsilonhat =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epsilonhat * L * f =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epsilonhat * L * fnueva =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplicadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector sumatorio columna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector sumatorio fila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplicadores Leontief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriz de emisiones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">directas e indirectas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplicadores de emisiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fagric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fmanuf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emisiones demanda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final agricultura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indirectas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emisiones demanda final manufacturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo directo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fprime =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fnuevaprime =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhat =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fnuevahat = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huellas de carbono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epsilon * L * fhat =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epsilon * L * fnuevahat =</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preparado por Renato Vargas</t>
   </si>
   <si>
-    <t xml:space="preserve">Economista / Analista de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://renatovargas.com</t>
+    <t xml:space="preserve">Consultor FMI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0_)"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +297,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
@@ -248,7 +321,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,7 +343,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2CEEF"/>
-        <bgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FFF2CFEE"/>
       </patternFill>
     </fill>
     <fill>
@@ -283,6 +356,18 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.7499"/>
         <bgColor rgb="FFA6C9EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.7999"/>
+        <bgColor rgb="FFF2CEEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFF2CFEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +404,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -337,40 +422,92 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -391,7 +528,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFE8E8E8"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -429,7 +566,7 @@
       <rgbColor rgb="FFA6CAEC"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF2CFEE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -449,250 +586,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Correlation HS2012-HS2007"/>
-      <sheetName val="HS12-HS07"/>
-      <sheetName val="HS07-BEC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Checklist"/>
-      <sheetName val="append"/>
-      <sheetName val="Internal Linkage"/>
-      <sheetName val="Table1.1"/>
-      <sheetName val="Table1.2"/>
-      <sheetName val="Table1.3"/>
-      <sheetName val="Table2.1"/>
-      <sheetName val="Table2.2"/>
-      <sheetName val="Fig2.1"/>
-      <sheetName val="Fig2.2a"/>
-      <sheetName val="Fig2.2b"/>
-      <sheetName val="35-sector"/>
-      <sheetName val="2000"/>
-      <sheetName val="2010"/>
-      <sheetName val="2011"/>
-      <sheetName val="2012"/>
-      <sheetName val="2013"/>
-      <sheetName val="2014"/>
-      <sheetName val="2015"/>
-      <sheetName val="2016"/>
-      <sheetName val="2017"/>
-      <sheetName val="m1-3legend"/>
-      <sheetName val="InterData"/>
-      <sheetName val="5-sector"/>
-      <sheetName val="Summary"/>
-      <sheetName val="countrycode"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="COFOG_ISIC3.1"/>
-      <sheetName val="ISIC3.1_CPC1.1"/>
-      <sheetName val="COFOG_ISIC3.1_CPC1.1"/>
-      <sheetName val="Sheet7"/>
-      <sheetName val="COICOP_CPC1.0_CPC1.1"/>
-      <sheetName val="Sheet6"/>
-      <sheetName val="Sheet5"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="HS02_CPC1.1_SITC3_ISIC3.1 (2)"/>
-      <sheetName val="HS02_CPC1.1_SITC3_ISIC3.1"/>
-      <sheetName val="CPC1.1_CPC1.0"/>
-      <sheetName val="CPC1.0_CPC1.1"/>
-      <sheetName val="sheet"/>
-      <sheetName val="ISIC3.0_ISIC3.1"/>
-      <sheetName val="ICP_COICOP"/>
-      <sheetName val="COICOP_CPC"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="2000"/>
-      <sheetName val="2010"/>
-      <sheetName val="2011"/>
-      <sheetName val="2012"/>
-      <sheetName val="2013"/>
-      <sheetName val="2014"/>
-      <sheetName val="2015"/>
-      <sheetName val="2016"/>
-      <sheetName val="2017"/>
-      <sheetName val="sectors"/>
-      <sheetName val="35-sector"/>
-      <sheetName val="13-sector VAX_G_2010"/>
-      <sheetName val="13-sector VAX_G_2011"/>
-      <sheetName val="13-sector VAX_G_2012"/>
-      <sheetName val="13-sector VAX_G_2013"/>
-      <sheetName val="13-sector VAX_G_2014"/>
-      <sheetName val="13-sector VAX_G_2015"/>
-      <sheetName val="13-sector VAX_G_2016"/>
-      <sheetName val="13-sector VAX_G_2017"/>
-      <sheetName val="Countries_RCA_VAX_G"/>
-      <sheetName val="RCA_VAX_G_All countries"/>
-      <sheetName val="By country_RCA_VAX_G"/>
-      <sheetName val="Colors"/>
-      <sheetName val="HE select"/>
-      <sheetName val="Fig. 1.2.3"/>
-      <sheetName val="Fig. 1.2.3.a"/>
-      <sheetName val="Fig. 1.2.3.b."/>
-      <sheetName val="Fig. 1.2.4."/>
-      <sheetName val="Fig. 1.2.4.a"/>
-      <sheetName val="Fig. 1.2.4.b"/>
-      <sheetName val="Fig. 1.3.1"/>
-      <sheetName val="Fig 1.3.2"/>
-      <sheetName val="Fig. 1.3.3"/>
-      <sheetName val="Fig. 1.3.4"/>
-      <sheetName val="Fig. 1.3.5"/>
-      <sheetName val="Fig. 1.3.6"/>
-      <sheetName val="Fig. 1.3.7"/>
-      <sheetName val="Fig. 1.3.8"/>
-      <sheetName val="Fig. 1.3.9"/>
-      <sheetName val="Fig. 1.3.10"/>
-      <sheetName val="Fig. 1.3.11"/>
-      <sheetName val="Fig. 1.3.12"/>
-      <sheetName val="Fig. 1.3.13"/>
-      <sheetName val="Table 1.3.1"/>
-      <sheetName val="Table 1.3.2"/>
-      <sheetName val="Table 1.3.3"/>
-      <sheetName val="Table 1.3.4"/>
-      <sheetName val="Table 1.3.5"/>
-      <sheetName val="Fig. 1.3.14"/>
-      <sheetName val="Table 1.3.6"/>
-      <sheetName val="Fig. 1.3.15"/>
-      <sheetName val="Table 1.3.7"/>
-      <sheetName val="countrycode"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -741,105 +634,11 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -852,21 +651,18 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
@@ -878,14 +674,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -893,7 +687,6 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
@@ -934,7 +727,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill>
@@ -942,7 +734,6 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -950,7 +741,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -958,7 +748,6 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -976,311 +765,855 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B3:G1048576"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B3:G136"/>
+  <sheetFormatPr defaultColWidth="8.37109375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.69"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <f aca="false">SUM(C4:E4)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4" t="n">
         <v>1700</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <f aca="false">SUM(C5:E5)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7" s="1" t="n">
         <v>650</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7" s="1" t="n">
         <v>1400</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="1" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8" s="1" t="n">
         <v>3150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="5" t="n" cm="1">
-        <f aca="true" t="array" ref="C12:D13" ca="1">IF(G4:G5=TRANSPOSE(G4:G5),G4:G5,0)</f>
+      <c r="C12" s="6" t="n">
+        <f aca="false" t="array" ref="C12:D13">IF(G4:G5=TRANSPOSE(G4:G5),G4:G5,0)</f>
         <v>1000</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <f aca="false" t="array" ref="C15:D16">MINVERSE(xhat)</f>
         <v>0.001</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="C16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>0.0005</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <f aca="false" t="array" ref="C18:D19">MMULT(Z,xhatinv)</f>
         <v>0.15</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <f aca="false" t="array" ref="C21:D22">_xlfn.MUNIT(2)</f>
         <v>1</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5" t="n">
+      <c r="C22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <f aca="false" t="array" ref="C24:D25">identity-REQ</f>
         <v>0.85</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="6" t="n">
         <v>-0.25</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="6" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="8" t="n">
         <f aca="false" t="array" ref="C27:D28">MINVERSE((identity-REQ))</f>
         <v>1.25412541254125</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="n">
         <v>0.33003300330033</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="8" t="n">
         <v>0.264026402640264</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="n">
         <v>1.12211221122112</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <f aca="false" t="array" ref="C30:C31">MMULT(L,fdem)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="0" t="s">
+      <c r="C33" s="6" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="6" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <f aca="false" t="array" ref="C36:C37">MMULT(L,fdemnew)</f>
+        <v>1247.52475247525</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="6" t="n">
+        <v>1841.58415841584</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <f aca="false" t="array" ref="C39:D40">IF(C36:C37=TRANSPOSE(C36:C37),C36:C37,0)</f>
+        <v>1247.52475247525</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>1841.58415841584</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <f aca="false" t="array" ref="C42:D43">MMULT(REQ,xnewdiag)</f>
+        <v>187.128712871287</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>460.39603960396</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>249.504950495049</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>92.0792079207921</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="E47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <f aca="false" t="array" ref="C48:D49">C42:D43</f>
+        <v>187.128712871287</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>460.39603960396</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <f aca="false" t="array" ref="E48:E49">C33:C34</f>
+        <v>600</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <f aca="false">SUM(C48:E48)</f>
+        <v>1247.52475247525</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>249.504950495049</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>92.0792079207921</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <f aca="false">SUM(C49:E49)</f>
+        <v>1841.58415841584</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="15" t="n">
+        <f aca="false">C52-SUM(C48:C49)</f>
+        <v>810.891089108911</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <f aca="false">D52-SUM(D48:D49)</f>
+        <v>1289.10891089109</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="14" t="n">
+        <f aca="false">G48</f>
+        <v>1247.52475247525</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <f aca="false">G49</f>
+        <v>1841.58415841584</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <f aca="false" t="array" ref="C56:C57">fdemnew-fdem</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C57" s="6" t="n">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <f aca="false" t="array" ref="C59:C60">xnew-xoriginal</f>
+        <v>247.524752475247</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="7" t="n">
+        <v>-158.415841584158</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <f aca="false" t="array" ref="C64:C65">deltafnew*C62</f>
+        <v>860</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>-688</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D70" s="17" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <f aca="false" t="array" ref="C39:D39">MMULT(C36:D36,C15:D16)</f>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="18" t="n">
+        <f aca="false" t="array" ref="C73:D73">MMULT(C70:D70,C15:D16)</f>
         <v>0.3</v>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D73" s="18" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="18" t="n">
+        <f aca="false" t="array" ref="C75:D76">IF(C73:D73=TRANSPOSE(C73:D73),C73:D73,0)</f>
+        <v>0.3</v>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="17" t="n">
+        <f aca="false" t="array" ref="C78:C79">MMULT(C75:D76,MMULT(C27:D28,E4:E5))</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="17" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81" s="18" t="n">
+        <f aca="false" t="array" ref="C81:C82">MMULT(C75:D76,MMULT(C27:D28,E48:E49))</f>
+        <v>374.257425742574</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="18" t="n">
+        <v>460.39603960396</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C92" s="8" t="n">
+        <f aca="false" t="array" ref="C92:D92">MMULT(C89:D89,C27:D28)</f>
+        <v>1.51815181518152</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>1.45214521452145</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" s="19" t="n">
+        <f aca="false" t="array" ref="C94:D95">MMULT(C75:D76,C27:D28)</f>
+        <v>0.376237623762376</v>
+      </c>
+      <c r="D94" s="19" t="n">
+        <v>0.099009900990099</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>0.066006600660066</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>0.280528052805281</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99" s="18" t="n">
+        <f aca="false" t="array" ref="C99:D99">MMULT(C89:D89,C94:D95)</f>
+        <v>0.442244224422442</v>
+      </c>
+      <c r="D99" s="18" t="n">
+        <v>0.37953795379538</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="4" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C108" s="18" t="n">
+        <f aca="false" t="array" ref="C108:C109">MMULT(C94:D95,C101:C102)</f>
+        <v>131.683168316832</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C109" s="18" t="n">
+        <v>23.1023102310231</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C111" s="18" t="n">
+        <f aca="false">SUM(C108:C109)</f>
+        <v>154.785478547855</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C113" s="18" t="n">
+        <f aca="false" t="array" ref="C113:C114">MMULT(C94:D95,C104:C105)</f>
+        <v>168.316831683168</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="18" t="n">
+        <v>476.897689768977</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C116" s="18" t="n">
+        <f aca="false">SUM(C113:C114)</f>
+        <v>645.214521452145</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <f aca="false" t="array" ref="C120:D120">TRANSPOSE(E4:E5)</f>
+        <v>350</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <f aca="false" t="array" ref="C122:D122">TRANSPOSE(E48:E49)</f>
+        <v>600</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C124" s="4" t="n">
+        <f aca="false" t="array" ref="C124:D125">IF(C120:D120=TRANSPOSE(C120:D120),C120:D120,0)</f>
+        <v>350</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C127" s="4" t="n">
+        <f aca="false" t="array" ref="C127:D128">IF(C122:D122=TRANSPOSE(C122:D122),C122:D122,0)</f>
+        <v>600</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C132" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C133" s="19" t="n">
+        <f aca="false" t="array" ref="C133:D133">MMULT(C73:D73,MMULT(C27:D28,C124:D125))</f>
+        <v>154.785478547855</v>
+      </c>
+      <c r="D133" s="19" t="n">
+        <v>645.214521452145</v>
+      </c>
+      <c r="E133" s="18" t="n">
+        <f aca="false">SUM(C133:D133)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C135" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136" s="19" t="n">
+        <f aca="false" t="array" ref="C136:D136">MMULT(C73:D73,MMULT(C27:D28,C127:D128))</f>
+        <v>265.346534653465</v>
+      </c>
+      <c r="D136" s="19" t="n">
+        <v>569.306930693069</v>
+      </c>
+      <c r="E136" s="18" t="n">
+        <f aca="false">SUM(C136:D136)</f>
+        <v>834.653465346535</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1298,27 +1631,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.94921875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>18</v>
+      <c r="A1" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="A2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="https://renatovargas.com"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/datos/ejemplos/insumo-producto-ambiental.xlsx
+++ b/datos/ejemplos/insumo-producto-ambiental.xlsx
@@ -463,6 +463,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -476,10 +480,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1007,13 +1007,13 @@
       <c r="B36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="10" t="n">
         <f aca="false" t="array" ref="C36:C37">MMULT(L,fdemnew)</f>
         <v>1247.52475247525</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="6" t="n">
+      <c r="C37" s="10" t="n">
         <v>1841.58415841584</v>
       </c>
     </row>
@@ -1041,11 +1041,11 @@
       <c r="B42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="11" t="n">
         <f aca="false" t="array" ref="C42:D43">MMULT(REQ,xnewdiag)</f>
         <v>187.128712871287</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="11" t="n">
         <v>460.39603960396</v>
       </c>
     </row>
@@ -1053,15 +1053,15 @@
       <c r="B43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="11" t="n">
         <v>249.504950495049</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="11" t="n">
         <v>92.0792079207921</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1083,18 +1083,18 @@
       <c r="B48" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C48" s="12" t="n">
+      <c r="C48" s="13" t="n">
         <f aca="false" t="array" ref="C48:D49">C42:D43</f>
         <v>187.128712871287</v>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D48" s="13" t="n">
         <v>460.39603960396</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="14" t="n">
         <f aca="false" t="array" ref="E48:E49">C33:C34</f>
         <v>600</v>
       </c>
-      <c r="G48" s="14" t="n">
+      <c r="G48" s="10" t="n">
         <f aca="false">SUM(C48:E48)</f>
         <v>1247.52475247525</v>
       </c>
@@ -1103,16 +1103,16 @@
       <c r="B49" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C49" s="12" t="n">
+      <c r="C49" s="13" t="n">
         <v>249.504950495049</v>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="13" t="n">
         <v>92.0792079207921</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="G49" s="14" t="n">
+      <c r="G49" s="10" t="n">
         <f aca="false">SUM(C49:E49)</f>
         <v>1841.58415841584</v>
       </c>
@@ -1137,11 +1137,11 @@
       <c r="B52" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="14" t="n">
+      <c r="C52" s="10" t="n">
         <f aca="false">G48</f>
         <v>1247.52475247525</v>
       </c>
-      <c r="D52" s="14" t="n">
+      <c r="D52" s="10" t="n">
         <f aca="false">G49</f>
         <v>1841.58415841584</v>
       </c>
@@ -1236,6 +1236,10 @@
         <v>30</v>
       </c>
     </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+    </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
         <v>31</v>
@@ -1297,7 +1301,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1487,7 +1491,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="12" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1556,7 +1560,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="11" t="s">
+      <c r="B130" s="12" t="s">
         <v>56</v>
       </c>
     </row>
